--- a/Packages/cn.etetet.twsmonster/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twsmonster/Luban/Config/Base/__tables__.xlsx
@@ -125,22 +125,22 @@
     <t>cn.etetet.twsmonster</t>
   </si>
   <si>
-    <t>Monster</t>
-  </si>
-  <si>
-    <t>cn.etetet.twsmonster.MonsterConfigCategory</t>
-  </si>
-  <si>
-    <t>MonsterConfig</t>
-  </si>
-  <si>
-    <t>..\..\..\..\cn.etetet.twsmonster\Luban\Config\Datas\Monster.xlsx</t>
+    <t>GameObjectPoolSettings</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmonster.GameObjectPoolSettingsConfigCategory</t>
+  </si>
+  <si>
+    <t>GameObjectPoolSettingsConfig</t>
+  </si>
+  <si>
+    <t>..\..\..\..\cn.etetet.twsmonster\Luban\Config\Datas\GameObjectPoolSettings.xlsx</t>
   </si>
   <si>
     <t>c</t>
   </si>
   <si>
-    <t>MonsterConfigCategory</t>
+    <t>GameObjectPoolSettingsConfigCategory</t>
   </si>
 </sst>
 </file>
@@ -1088,8 +1088,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1233,7 +1233,7 @@
         <v>DemoConfigCategory</v>
       </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" customFormat="1" spans="2:13">
       <c r="B5" t="s">
         <v>31</v>
       </c>
@@ -1246,7 +1246,7 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="b">
+      <c r="F5" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
@@ -1258,9 +1258,6 @@
       <c r="M5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" spans="6:6">
-      <c r="F6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
